--- a/Openpyxl 10.12.24.xlsx
+++ b/Openpyxl 10.12.24.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Basics" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="410">
   <si>
     <t>Изваждане на количества от склад</t>
   </si>
@@ -7219,18 +7219,1277 @@
   </si>
   <si>
     <t>Как може да кажем append from C13 for example</t>
+  </si>
+  <si>
+    <t>&lt;generator object Worksheet._cells_by_row at 0x00000000032E90B0&gt;</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'6607005', 'Телефонен проводник ШТРВШ 8х0.25', 'м', 100, None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ws_source</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iter_rows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ws_source</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iter_rows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>values_only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=True))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>el</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ws_source</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iter_rows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(values_only=True):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>el</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>el</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ws_source</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iter_rows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>():</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            print(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>el</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;Cell 'КАБЕЛИ И ПРОВОДНИЦИ'.A727&gt;, &lt;Cell 'КАБЕЛИ И ПРОВОДНИЦИ'.B727&gt;, &lt;Cell 'КАБЕЛИ И ПРОВОДНИЦИ'.C727&gt;, &lt;Cell 'КАБЕЛИ И ПРОВОДНИЦИ'.D727&gt;, &lt;Cell 'КАБЕЛИ И ПРОВОДНИЦИ'.E727&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>merge.py</t>
+  </si>
+  <si>
+    <t>1. What does iter_rows() return?</t>
+  </si>
+  <si>
+    <t>Each row contains the cells from that row.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">iter_rows() returns an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iterator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that gives you the rows of the worksheet </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>one by one</t>
+    </r>
+  </si>
+  <si>
+    <t>Without values_only=True, each row contains Cell objects.</t>
+  </si>
+  <si>
+    <t>for row in ws.iter_rows():</t>
+  </si>
+  <si>
+    <t>(&lt;Cell 'Sheet1'.A1&gt;, &lt;Cell 'Sheet1'.B1&gt;, &lt;Cell 'Sheet1'.C1&gt;)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7D7DFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in ws.iter_rows():</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So every </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7D7DFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is a real Excel cell object</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7D7DFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> е клетката А1 като обект</t>
+    </r>
+  </si>
+  <si>
+    <t>2. What does values_only=True do?</t>
+  </si>
+  <si>
+    <t>When you use:</t>
+  </si>
+  <si>
+    <t>iter_rows(values_only=True)</t>
+  </si>
+  <si>
+    <t>you tell openpyxl:</t>
+  </si>
+  <si>
+    <t>"Don't give me Cell objects. Give me only the values inside them."</t>
+  </si>
+  <si>
+    <t>So instead of this:</t>
+  </si>
+  <si>
+    <t>&lt;Cell 'Sheet1'.A1&gt;</t>
+  </si>
+  <si>
+    <t>you get:</t>
+  </si>
+  <si>
+    <t>9215400007'</t>
+  </si>
+  <si>
+    <t>3. Difference with and without values_only=True</t>
+  </si>
+  <si>
+    <t>(&lt;Cell 'Sheet1'.A1&gt;, &lt;Cell 'Sheet1'.B1&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    print(row[0].value)</t>
+  </si>
+  <si>
+    <t>to access the value</t>
+  </si>
+  <si>
+    <t>to access the cell</t>
+  </si>
+  <si>
+    <t>for row in ws.iter_rows(values_only=True):</t>
+  </si>
+  <si>
+    <t>to access the value with values_only</t>
+  </si>
+  <si>
+    <t>('9215400007', 'Щепсел бакелит')</t>
+  </si>
+  <si>
+    <t>No .value needed.</t>
+  </si>
+  <si>
+    <t>4. What becomes i and row here?</t>
+  </si>
+  <si>
+    <t>in the loop:</t>
+  </si>
+  <si>
+    <t>('9215400007', 'Product A', 'бр')</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'9215400008', 'Product B', 'бр')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'9215400007', 'Product A', 'бр'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Part 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iter_rows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(...) produces rows one by one:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Part 2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>enumerate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(...)</t>
+    </r>
+  </si>
+  <si>
+    <t>enumerate() adds a counter</t>
+  </si>
+  <si>
+    <t>So each iteration becomes:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ('9215400008', 'Product B', 'бр')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ('9215400007', 'Product A', 'бр')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in enumerate(ws_source.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iter_rows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(values_only=True), start=1):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF002060"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = row number counter</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = tuple containing row values</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">            # this 3 lines strips column A - row[0]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">               </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[0] = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[0].</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strip</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">            if </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[0] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>is not None and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA47A20"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isinstance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDA7BB9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>row</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[0], </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF179A77"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>):</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Why did you convert row to a list?</t>
+  </si>
+  <si>
+    <t>Originally row is a tuple</t>
+  </si>
+  <si>
+    <t>('9215400007', 'Product A', 'бр'</t>
+  </si>
+  <si>
+    <t>Tuples are immutable so you cannot do:</t>
+  </si>
+  <si>
+    <t>row[0] = "new"</t>
+  </si>
+  <si>
+    <t>So you convert it:</t>
+  </si>
+  <si>
+    <t>row = list(row)</t>
+  </si>
+  <si>
+    <t>Now:</t>
+  </si>
+  <si>
+    <t>row[0] = row[0].strip()</t>
+  </si>
+  <si>
+    <t>6. Visual summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> iter_rows(values_only=True)</t>
+  </si>
+  <si>
+    <t>With:</t>
+  </si>
+  <si>
+    <t>Excel row:</t>
+  </si>
+  <si>
+    <t>Product A</t>
+  </si>
+  <si>
+    <t>becomes:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="35" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7496,6 +8755,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7D7DFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -7612,12 +8879,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -7629,38 +8895,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7671,8 +8944,9 @@
     <mruColors>
       <color rgb="FFA47A20"/>
       <color rgb="FF179A77"/>
+      <color rgb="FFDA7BB9"/>
+      <color rgb="FF7D7DFF"/>
       <color rgb="FFA626A4"/>
-      <color rgb="FFDA7BB9"/>
     </mruColors>
   </colors>
   <extLst>
@@ -7791,13 +9065,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>193431</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>35169</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>179</xdr:row>
       <xdr:rowOff>23446</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7838,13 +9112,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>274698</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>35963</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>276286</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>179</xdr:row>
       <xdr:rowOff>12517</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7885,13 +9159,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>111369</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>17585</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>5862</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>179</xdr:row>
       <xdr:rowOff>11723</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7932,13 +9206,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>532606</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>18379</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>534194</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>179</xdr:row>
       <xdr:rowOff>6655</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7979,13 +9253,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>29308</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>486508</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>164123</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8026,13 +9300,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>105509</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>176</xdr:row>
       <xdr:rowOff>169983</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>11724</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>41029</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8073,13 +9347,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>480647</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>183</xdr:row>
       <xdr:rowOff>23446</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>184</xdr:row>
       <xdr:rowOff>134816</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8120,13 +9394,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>211016</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>111369</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>46892</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8167,13 +9441,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>29308</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>46892</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>580292</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>52754</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8214,13 +9488,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>205154</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>93785</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>5862</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>52753</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8261,13 +9535,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>427892</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>46892</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>128954</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>5861</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8308,13 +9582,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>468924</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>162</xdr:row>
       <xdr:rowOff>123091</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>603739</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>52753</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8355,13 +9629,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>351692</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>167</xdr:row>
       <xdr:rowOff>164123</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>603738</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>168</xdr:row>
       <xdr:rowOff>134815</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8402,13 +9676,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>480646</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>166</xdr:row>
       <xdr:rowOff>105509</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>167</xdr:row>
       <xdr:rowOff>58615</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8449,13 +9723,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>281354</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>11723</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>562708</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>123092</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8496,13 +9770,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>298938</xdr:colOff>
-      <xdr:row>266</xdr:row>
+      <xdr:row>358</xdr:row>
       <xdr:rowOff>117231</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>545123</xdr:colOff>
-      <xdr:row>267</xdr:row>
+      <xdr:row>359</xdr:row>
       <xdr:rowOff>35169</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8543,13 +9817,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>29308</xdr:colOff>
-      <xdr:row>265</xdr:row>
+      <xdr:row>357</xdr:row>
       <xdr:rowOff>111370</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>539262</xdr:colOff>
-      <xdr:row>265</xdr:row>
+      <xdr:row>357</xdr:row>
       <xdr:rowOff>112958</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8590,13 +9864,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>29308</xdr:colOff>
-      <xdr:row>266</xdr:row>
+      <xdr:row>358</xdr:row>
       <xdr:rowOff>99646</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>539262</xdr:colOff>
-      <xdr:row>266</xdr:row>
+      <xdr:row>358</xdr:row>
       <xdr:rowOff>101234</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -8679,7 +9953,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8711,10 +9985,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8746,7 +10019,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -8922,306 +10194,306 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="B9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="B10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="B12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="B16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2">
       <c r="B17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2">
       <c r="B18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2">
       <c r="B19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2">
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2">
       <c r="B23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2">
       <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2">
       <c r="B26" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2">
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2">
       <c r="B29" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2">
       <c r="B31" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2">
       <c r="B32" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2">
       <c r="B33" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2">
       <c r="B35" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2">
       <c r="B36" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2">
       <c r="B37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2">
       <c r="B39" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2">
       <c r="B40" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2">
       <c r="B41" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2">
       <c r="B42" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:2">
       <c r="B43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2">
       <c r="B44" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2">
       <c r="B45" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:2">
       <c r="B46" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:2">
       <c r="B47" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2">
       <c r="B48" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:2">
       <c r="B50" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:2">
       <c r="B51" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2">
       <c r="B53" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:2">
       <c r="B54" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:2">
       <c r="B55" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:2">
       <c r="B56" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:2">
       <c r="B57" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2">
       <c r="B58" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:2">
       <c r="B60" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:2">
       <c r="B61" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:2">
       <c r="B63" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:2">
       <c r="B64" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="B65" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7">
       <c r="B66" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7">
       <c r="B67" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7">
       <c r="B68" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7">
       <c r="A71" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7">
       <c r="B73" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7">
       <c r="B75" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7">
       <c r="B76" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7">
       <c r="B77" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7">
       <c r="B79" t="s">
         <v>326</v>
       </c>
@@ -9232,64 +10504,64 @@
         <v>247</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7">
       <c r="B80" t="s">
         <v>331</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
-      <c r="F80" s="40" t="s">
+      <c r="F80" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="G80" s="40" t="s">
+      <c r="G80" s="39" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:7">
       <c r="B81" t="s">
         <v>330</v>
       </c>
       <c r="E81">
         <v>2</v>
       </c>
-      <c r="F81" s="40" t="s">
+      <c r="F81" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="G81" s="40">
+      <c r="G81" s="39">
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:7">
       <c r="B82" t="s">
         <v>332</v>
       </c>
       <c r="E82">
         <v>3</v>
       </c>
-      <c r="F82" s="40" t="s">
+      <c r="F82" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="G82" s="40">
+      <c r="G82" s="39">
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:7">
       <c r="B83" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="F84" s="41" t="s">
+    <row r="84" spans="2:7">
+      <c r="F84" s="40" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:7">
       <c r="B85" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:7">
       <c r="B86" t="s">
         <v>334</v>
       </c>
@@ -9301,134 +10573,271 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:T300"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:T392"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="4" max="4" width="8.88671875" customWidth="1"/>
     <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" s="6" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="9" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="9" t="s">
         <v>238</v>
       </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
       <c r="J8" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+    <row r="9" spans="1:10">
+      <c r="B9" s="9" t="s">
         <v>224</v>
       </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11"/>
       <c r="J9" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+    <row r="10" spans="1:10">
+      <c r="B10" s="9" t="s">
         <v>227</v>
       </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="11"/>
       <c r="J10" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+    <row r="11" spans="1:10">
+      <c r="B11" s="9" t="s">
         <v>226</v>
       </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="11"/>
       <c r="J11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+    <row r="12" spans="1:10">
+      <c r="B12" s="9" t="s">
         <v>241</v>
       </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="11"/>
       <c r="J12" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+    <row r="13" spans="1:10">
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="9" t="s">
         <v>229</v>
       </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11"/>
       <c r="J14" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+    <row r="15" spans="1:10">
+      <c r="B15" s="9" t="s">
         <v>228</v>
       </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11"/>
       <c r="J15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+    <row r="16" spans="1:10">
+      <c r="B16" s="9" t="s">
         <v>54</v>
       </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
       <c r="J16" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+    <row r="17" spans="2:20">
+      <c r="B17" s="9" t="s">
         <v>235</v>
       </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
       <c r="J17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
+    <row r="18" spans="2:20">
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="2:20">
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="2:20">
+      <c r="B20" s="9" t="s">
         <v>236</v>
       </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="11"/>
       <c r="J20" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+    <row r="21" spans="2:20">
+      <c r="B21" s="9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+    </row>
+    <row r="22" spans="2:20">
+      <c r="B22" s="9" t="s">
         <v>230</v>
       </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="11"/>
       <c r="J22" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+    <row r="23" spans="2:20">
+      <c r="B23" s="9" t="s">
         <v>190</v>
       </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11"/>
       <c r="J23" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>237</v>
-      </c>
-      <c r="H24" t="s">
+    <row r="24" spans="2:20">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="11" t="s">
         <v>244</v>
       </c>
       <c r="I24" t="s">
@@ -9438,1838 +10847,2425 @@
         <v>242</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>56</v>
-      </c>
+    <row r="25" spans="2:20">
+      <c r="B25" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="11"/>
       <c r="J25" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B26" s="25" t="s">
+    <row r="26" spans="2:20">
+      <c r="B26" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="11"/>
+    </row>
+    <row r="27" spans="2:20">
+      <c r="B27" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="2:20">
+      <c r="B28" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="2:20">
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="11"/>
+    </row>
+    <row r="30" spans="2:20">
+      <c r="B30" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="11"/>
+    </row>
+    <row r="31" spans="2:20">
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="11"/>
+    </row>
+    <row r="32" spans="2:20">
+      <c r="B32" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="J26" t="s">
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="11"/>
+      <c r="J32" t="s">
         <v>146</v>
       </c>
-      <c r="O26" s="35" t="s">
+      <c r="O32" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="P26" s="35" t="s">
+      <c r="P32" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="Q26" s="35" t="s">
+      <c r="Q32" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="R26" s="35" t="s">
+      <c r="R32" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="S26" s="35" t="s">
+      <c r="S32" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="T26" s="35" t="s">
+      <c r="T32" s="34" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+    <row r="33" spans="2:20">
+      <c r="B33" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="J27" t="s">
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="11"/>
+      <c r="J33" t="s">
         <v>147</v>
       </c>
-      <c r="O27" s="35">
+      <c r="O33" s="34">
         <v>9215400007</v>
       </c>
-      <c r="P27" s="36" t="s">
+      <c r="P33" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="Q27" s="35" t="s">
+      <c r="Q33" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="R27" s="35">
+      <c r="R33" s="34">
         <v>126</v>
       </c>
-      <c r="S27" s="35" t="s">
+      <c r="S33" s="34" t="s">
         <v>251</v>
       </c>
-      <c r="T27" s="35" t="s">
+      <c r="T33" s="34" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B30" s="4" t="s">
+    <row r="34" spans="2:20">
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="11"/>
+    </row>
+    <row r="35" spans="2:20">
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="11"/>
+    </row>
+    <row r="36" spans="2:20">
+      <c r="B36" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="J30" t="s">
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="11"/>
+      <c r="J36" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+    <row r="37" spans="2:20">
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="14"/>
+    </row>
+    <row r="39" spans="2:20">
+      <c r="B39" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20">
+      <c r="C40" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20">
+      <c r="B42" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20">
+      <c r="C43" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20">
+      <c r="B45" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20">
+      <c r="C46" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20">
+      <c r="D47" s="42" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20">
+      <c r="D48" s="42"/>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" t="s">
+        <v>346</v>
+      </c>
+      <c r="D49" s="42"/>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" t="s">
+        <v>347</v>
+      </c>
+      <c r="D50" s="42"/>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="D51" s="42" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="D52" s="42"/>
+    </row>
+    <row r="53" spans="2:8">
+      <c r="B53" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D53" s="42"/>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="C54" t="s">
+        <v>352</v>
+      </c>
+      <c r="D54" s="42"/>
+    </row>
+    <row r="55" spans="2:8">
+      <c r="C55" t="s">
+        <v>351</v>
+      </c>
+      <c r="D55" s="42"/>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="D56" s="42"/>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="C57" t="s">
+        <v>353</v>
+      </c>
+      <c r="D57" s="42"/>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="D58" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
+      <c r="D59" s="42"/>
+      <c r="E59" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8">
+      <c r="D60" s="42"/>
+      <c r="E60" t="s">
+        <v>288</v>
+      </c>
+      <c r="H60" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8">
+      <c r="D61" s="42"/>
+    </row>
+    <row r="62" spans="2:8">
+      <c r="D62" s="42"/>
+      <c r="E62" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
+      <c r="D63" s="42"/>
+      <c r="E63" s="42" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
+      <c r="B64" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D64" s="42"/>
+    </row>
+    <row r="65" spans="2:9">
+      <c r="C65" t="s">
+        <v>360</v>
+      </c>
+      <c r="D65" s="42"/>
+    </row>
+    <row r="66" spans="2:9">
+      <c r="D66" s="42" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9">
+      <c r="C67" t="s">
+        <v>362</v>
+      </c>
+      <c r="D67" s="42"/>
+    </row>
+    <row r="68" spans="2:9">
+      <c r="D68" s="42" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9">
+      <c r="C69" t="s">
+        <v>364</v>
+      </c>
+      <c r="D69" s="42"/>
+    </row>
+    <row r="70" spans="2:9">
+      <c r="D70" s="42" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9">
+      <c r="C71" t="s">
+        <v>366</v>
+      </c>
+      <c r="D71" s="42"/>
+    </row>
+    <row r="72" spans="2:9">
+      <c r="D72" s="44" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9">
+      <c r="D73" s="44"/>
+    </row>
+    <row r="74" spans="2:9">
+      <c r="B74" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D74" s="44"/>
+    </row>
+    <row r="75" spans="2:9">
+      <c r="B75" s="3"/>
+      <c r="C75" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D75" s="44"/>
+      <c r="G75" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9">
+      <c r="B76" s="3"/>
+      <c r="C76" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D76" s="45"/>
+      <c r="E76" s="8"/>
+      <c r="G76" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="H76" s="7"/>
+      <c r="I76" s="8"/>
+    </row>
+    <row r="77" spans="2:9">
+      <c r="B77" s="3"/>
+      <c r="C77" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="D77" s="46"/>
+      <c r="E77" s="14"/>
+      <c r="G77" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="H77" s="13"/>
+      <c r="I77" s="14"/>
+    </row>
+    <row r="78" spans="2:9">
+      <c r="B78" s="3"/>
+      <c r="D78" s="44"/>
+    </row>
+    <row r="79" spans="2:9">
+      <c r="B79" s="3"/>
+      <c r="C79" s="43" t="s">
+        <v>369</v>
+      </c>
+      <c r="D79" s="44"/>
+      <c r="G79" s="43" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9">
+      <c r="B80" s="3"/>
+      <c r="D80" s="44"/>
+    </row>
+    <row r="81" spans="2:6">
+      <c r="B81" s="3"/>
+      <c r="C81" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D81" s="44"/>
+    </row>
+    <row r="82" spans="2:6">
+      <c r="B82" s="3"/>
+      <c r="C82" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D82" s="45"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="8"/>
+    </row>
+    <row r="83" spans="2:6">
+      <c r="B83" s="3"/>
+      <c r="C83" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="D83" s="46"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="14"/>
+    </row>
+    <row r="84" spans="2:6">
+      <c r="C84" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="D84" s="44"/>
+    </row>
+    <row r="85" spans="2:6">
+      <c r="C85" s="43" t="s">
+        <v>375</v>
+      </c>
+      <c r="D85" s="42"/>
+    </row>
+    <row r="86" spans="2:6">
+      <c r="C86" s="43"/>
+      <c r="D86" s="42"/>
+    </row>
+    <row r="87" spans="2:6">
+      <c r="B87" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C87" s="43"/>
+      <c r="D87" s="42"/>
+    </row>
+    <row r="88" spans="2:6">
+      <c r="C88" t="s">
+        <v>378</v>
+      </c>
+      <c r="D88" s="42"/>
+    </row>
+    <row r="89" spans="2:6">
+      <c r="D89" s="42" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6">
+      <c r="D90" s="42"/>
+    </row>
+    <row r="91" spans="2:6">
+      <c r="D91" s="42" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6">
+      <c r="D92" s="42" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
+      <c r="D93" s="42"/>
+    </row>
+    <row r="94" spans="2:6">
+      <c r="C94" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="D94" s="42"/>
+    </row>
+    <row r="95" spans="2:6">
+      <c r="D95" s="42" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6">
+      <c r="D96" s="42" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5">
+      <c r="D97" s="42"/>
+    </row>
+    <row r="98" spans="2:5">
+      <c r="C98" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="D98" s="42"/>
+    </row>
+    <row r="99" spans="2:5">
+      <c r="C99" s="42"/>
+      <c r="D99" s="42" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5">
+      <c r="C100" s="42"/>
+      <c r="D100" s="42"/>
+    </row>
+    <row r="101" spans="2:5">
+      <c r="C101" s="42"/>
+      <c r="D101" s="42" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5">
+      <c r="C102" s="42"/>
+      <c r="D102" s="42"/>
+      <c r="E102" s="42" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5">
+      <c r="D103" s="42"/>
+      <c r="E103" s="42" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5">
+      <c r="D104" s="42"/>
+    </row>
+    <row r="105" spans="2:5">
+      <c r="B105" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D105" s="42"/>
+    </row>
+    <row r="106" spans="2:5">
+      <c r="C106" t="s">
+        <v>396</v>
+      </c>
+      <c r="D106" s="42"/>
+    </row>
+    <row r="107" spans="2:5">
+      <c r="D107" s="42" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5">
+      <c r="C108" t="s">
+        <v>398</v>
+      </c>
+      <c r="D108" s="42"/>
+    </row>
+    <row r="109" spans="2:5">
+      <c r="D109" s="42" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5">
+      <c r="C110" t="s">
+        <v>400</v>
+      </c>
+      <c r="D110" s="42"/>
+    </row>
+    <row r="111" spans="2:5">
+      <c r="D111" s="42" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5">
+      <c r="C112" t="s">
+        <v>402</v>
+      </c>
+      <c r="D112" s="42"/>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="D113" s="42" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="D114" s="42"/>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="B115" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D115" s="42"/>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="C116" t="s">
+        <v>406</v>
+      </c>
+      <c r="D116" s="42"/>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="D117" s="42" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="C118" t="s">
+        <v>407</v>
+      </c>
+      <c r="D118" s="42"/>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="D119" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="E119" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="F119" s="34" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="D120" s="47">
+        <v>9215400007</v>
+      </c>
+      <c r="E120" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="F120" s="34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="C121" t="s">
+        <v>409</v>
+      </c>
+      <c r="D121" s="42"/>
+    </row>
+    <row r="122" spans="1:15">
+      <c r="D122" s="42" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
+      <c r="A125" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B34" s="7" t="s">
+    <row r="126" spans="1:15">
+      <c r="B126" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="9"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B35" s="10" t="s">
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="7"/>
+      <c r="J126" s="7"/>
+      <c r="K126" s="7"/>
+      <c r="L126" s="8"/>
+    </row>
+    <row r="127" spans="1:15">
+      <c r="B127" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="12"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B36" s="10"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="L36" s="12"/>
-      <c r="N36" s="18" t="s">
+      <c r="C127" s="10"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="10"/>
+      <c r="F127" s="10"/>
+      <c r="G127" s="10"/>
+      <c r="H127" s="10"/>
+      <c r="I127" s="10"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="10"/>
+      <c r="L127" s="11"/>
+    </row>
+    <row r="128" spans="1:15">
+      <c r="B128" s="9"/>
+      <c r="C128" s="10"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="10"/>
+      <c r="F128" s="10"/>
+      <c r="G128" s="10"/>
+      <c r="H128" s="10"/>
+      <c r="I128" s="10"/>
+      <c r="L128" s="11"/>
+      <c r="N128" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="O36" s="22" t="s">
+      <c r="O128" s="21" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B37" s="16" t="s">
+    <row r="129" spans="2:18">
+      <c r="B129" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="L37" s="12"/>
-      <c r="N37" s="19" t="s">
+      <c r="C129" s="10"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="10"/>
+      <c r="F129" s="10"/>
+      <c r="G129" s="10"/>
+      <c r="H129" s="10"/>
+      <c r="L129" s="11"/>
+      <c r="N129" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="O37" s="23" t="s">
+      <c r="O129" s="22" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B38" s="10"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="L38" s="12"/>
-      <c r="N38" s="20" t="s">
+    <row r="130" spans="2:18">
+      <c r="B130" s="9"/>
+      <c r="C130" s="10"/>
+      <c r="D130" s="10"/>
+      <c r="E130" s="10"/>
+      <c r="F130" s="10"/>
+      <c r="G130" s="10"/>
+      <c r="H130" s="10"/>
+      <c r="L130" s="11"/>
+      <c r="N130" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="O130" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B39" s="10" t="s">
+    <row r="131" spans="2:18">
+      <c r="B131" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="L39" s="12"/>
-      <c r="N39" s="21" t="s">
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
+      <c r="G131" s="10"/>
+      <c r="H131" s="10"/>
+      <c r="L131" s="11"/>
+      <c r="N131" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="O39" s="24" t="s">
+      <c r="O131" s="23" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B40" s="10" t="s">
+    <row r="132" spans="2:18">
+      <c r="B132" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="12"/>
-      <c r="N40" s="25"/>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B41" s="10" t="s">
+      <c r="C132" s="10"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10"/>
+      <c r="F132" s="10"/>
+      <c r="G132" s="10"/>
+      <c r="H132" s="10"/>
+      <c r="I132" s="10"/>
+      <c r="J132" s="10"/>
+      <c r="K132" s="10"/>
+      <c r="L132" s="11"/>
+      <c r="N132" s="24"/>
+    </row>
+    <row r="133" spans="2:18">
+      <c r="B133" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="17" t="s">
+      <c r="C133" s="10"/>
+      <c r="D133" s="10"/>
+      <c r="E133" s="10"/>
+      <c r="F133" s="10"/>
+      <c r="G133" s="10"/>
+      <c r="H133" s="10"/>
+      <c r="I133" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="12"/>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B42" s="10"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="12"/>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B43" s="10" t="s">
+      <c r="J133" s="10"/>
+      <c r="K133" s="10"/>
+      <c r="L133" s="11"/>
+    </row>
+    <row r="134" spans="2:18">
+      <c r="B134" s="9"/>
+      <c r="C134" s="10"/>
+      <c r="D134" s="10"/>
+      <c r="E134" s="10"/>
+      <c r="F134" s="10"/>
+      <c r="G134" s="10"/>
+      <c r="H134" s="10"/>
+      <c r="I134" s="10"/>
+      <c r="J134" s="10"/>
+      <c r="K134" s="10"/>
+      <c r="L134" s="11"/>
+    </row>
+    <row r="135" spans="2:18">
+      <c r="B135" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="17" t="s">
+      <c r="C135" s="10"/>
+      <c r="D135" s="10"/>
+      <c r="E135" s="10"/>
+      <c r="F135" s="10"/>
+      <c r="G135" s="10"/>
+      <c r="H135" s="10"/>
+      <c r="I135" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="12"/>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B44" s="10" t="s">
+      <c r="K135" s="10"/>
+      <c r="L135" s="11"/>
+    </row>
+    <row r="136" spans="2:18">
+      <c r="B136" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="12"/>
-      <c r="N44" s="11" t="s">
+      <c r="C136" s="10"/>
+      <c r="D136" s="10"/>
+      <c r="E136" s="10"/>
+      <c r="F136" s="10"/>
+      <c r="G136" s="10"/>
+      <c r="H136" s="10"/>
+      <c r="J136" s="10"/>
+      <c r="K136" s="10"/>
+      <c r="L136" s="11"/>
+      <c r="N136" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="O44" s="11" t="s">
+      <c r="O136" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="P44" s="11" t="s">
+      <c r="P136" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="Q44" s="28" t="s">
+      <c r="Q136" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="R44" s="12" t="s">
+      <c r="R136" s="11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B45" s="10"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="12"/>
-      <c r="N45" s="29">
+    <row r="137" spans="2:18">
+      <c r="B137" s="9"/>
+      <c r="C137" s="10"/>
+      <c r="D137" s="10"/>
+      <c r="E137" s="10"/>
+      <c r="F137" s="10"/>
+      <c r="G137" s="10"/>
+      <c r="I137" s="10"/>
+      <c r="J137" s="10"/>
+      <c r="K137" s="10"/>
+      <c r="L137" s="11"/>
+      <c r="N137" s="28">
         <v>764500</v>
       </c>
-      <c r="O45" s="27" t="s">
+      <c r="O137" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="P45" s="26" t="s">
+      <c r="P137" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="Q45" s="26">
+      <c r="Q137" s="25">
         <v>20</v>
       </c>
-      <c r="R45" s="26">
+      <c r="R137" s="25">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B46" s="10" t="s">
+    <row r="138" spans="2:18">
+      <c r="B138" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="12"/>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B47" s="10" t="s">
+      <c r="C138" s="10"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
+      <c r="G138" s="10"/>
+      <c r="I138" s="10"/>
+      <c r="K138" s="10"/>
+      <c r="L138" s="11"/>
+    </row>
+    <row r="139" spans="2:18">
+      <c r="B139" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11" t="s">
+      <c r="C139" s="10"/>
+      <c r="D139" s="10"/>
+      <c r="E139" s="10"/>
+      <c r="G139" s="10"/>
+      <c r="H139" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="12"/>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B48" s="10" t="s">
+      <c r="I139" s="10"/>
+      <c r="J139" s="10"/>
+      <c r="K139" s="10"/>
+      <c r="L139" s="11"/>
+    </row>
+    <row r="140" spans="2:18">
+      <c r="B140" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="25" t="s">
+      <c r="C140" s="10"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10"/>
+      <c r="G140" s="10"/>
+      <c r="H140" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="I48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="12"/>
-    </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B49" s="10" t="s">
+      <c r="I140" s="10"/>
+      <c r="K140" s="10"/>
+      <c r="L140" s="11"/>
+    </row>
+    <row r="141" spans="2:18">
+      <c r="B141" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="12"/>
-    </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B50" s="10"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" t="s">
+      <c r="C141" s="10"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="10"/>
+      <c r="F141" s="10"/>
+      <c r="G141" s="10"/>
+      <c r="H141" s="10"/>
+      <c r="I141" s="10"/>
+      <c r="J141" s="10"/>
+      <c r="K141" s="27"/>
+      <c r="L141" s="11"/>
+    </row>
+    <row r="142" spans="2:18">
+      <c r="B142" s="9"/>
+      <c r="C142" s="10"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
+      <c r="G142" s="10"/>
+      <c r="H142" t="s">
         <v>176</v>
       </c>
-      <c r="I50" s="30"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-    </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B51" s="10" t="s">
+      <c r="I142" s="29"/>
+      <c r="J142" s="30"/>
+      <c r="K142" s="30"/>
+      <c r="L142" s="30"/>
+    </row>
+    <row r="143" spans="2:18">
+      <c r="B143" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="12"/>
-    </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B52" s="10" t="s">
+      <c r="C143" s="10"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10"/>
+      <c r="F143" s="10"/>
+      <c r="G143" s="10"/>
+      <c r="I143" s="10"/>
+      <c r="J143" s="10"/>
+      <c r="K143" s="10"/>
+      <c r="L143" s="11"/>
+    </row>
+    <row r="144" spans="2:18">
+      <c r="B144" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11">
+      <c r="C144" s="10"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="10"/>
+      <c r="F144" s="10"/>
+      <c r="G144" s="10"/>
+      <c r="H144" s="10">
         <v>764500</v>
       </c>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="12"/>
-    </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B53" s="10" t="s">
+      <c r="I144" s="10"/>
+      <c r="J144" s="10"/>
+      <c r="K144" s="10"/>
+      <c r="L144" s="11"/>
+    </row>
+    <row r="145" spans="2:16">
+      <c r="B145" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11" t="s">
+      <c r="C145" s="10"/>
+      <c r="D145" s="10"/>
+      <c r="E145" s="10"/>
+      <c r="F145" s="10"/>
+      <c r="G145" s="10"/>
+      <c r="H145" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="12"/>
-      <c r="N53" s="7" t="s">
+      <c r="I145" s="10"/>
+      <c r="J145" s="10"/>
+      <c r="K145" s="10"/>
+      <c r="L145" s="11"/>
+      <c r="N145" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="O53" s="8"/>
-      <c r="P53" s="9"/>
-    </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B54" s="10" t="s">
+      <c r="O145" s="7"/>
+      <c r="P145" s="8"/>
+    </row>
+    <row r="146" spans="2:16">
+      <c r="B146" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11" t="s">
+      <c r="C146" s="10"/>
+      <c r="D146" s="10"/>
+      <c r="E146" s="10"/>
+      <c r="F146" s="10"/>
+      <c r="G146" s="10"/>
+      <c r="H146" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="12"/>
-      <c r="N54" s="13" t="s">
+      <c r="I146" s="10"/>
+      <c r="K146" s="10"/>
+      <c r="L146" s="11"/>
+      <c r="N146" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="O54" s="14"/>
-      <c r="P54" s="15"/>
-    </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B55" s="10"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="12"/>
-    </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B56" s="10" t="s">
+      <c r="O146" s="13"/>
+      <c r="P146" s="14"/>
+    </row>
+    <row r="147" spans="2:16">
+      <c r="B147" s="9"/>
+      <c r="C147" s="10"/>
+      <c r="D147" s="10"/>
+      <c r="E147" s="10"/>
+      <c r="F147" s="10"/>
+      <c r="G147" s="10"/>
+      <c r="I147" s="10"/>
+      <c r="J147" s="10"/>
+      <c r="K147" s="10"/>
+      <c r="L147" s="11"/>
+    </row>
+    <row r="148" spans="2:16">
+      <c r="B148" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="12"/>
-    </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B57" s="10" t="s">
+      <c r="C148" s="10"/>
+      <c r="D148" s="10"/>
+      <c r="E148" s="10"/>
+      <c r="F148" s="10"/>
+      <c r="G148" s="10"/>
+      <c r="H148" s="10"/>
+      <c r="I148" s="10"/>
+      <c r="J148" s="10"/>
+      <c r="K148" s="10"/>
+      <c r="L148" s="11"/>
+    </row>
+    <row r="149" spans="2:16">
+      <c r="B149" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="12"/>
-    </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B58" s="10"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
-      <c r="L58" s="12"/>
-    </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B59" s="10" t="s">
+      <c r="C149" s="10"/>
+      <c r="D149" s="10"/>
+      <c r="E149" s="10"/>
+      <c r="F149" s="10"/>
+      <c r="H149" s="10"/>
+      <c r="I149" s="10"/>
+      <c r="J149" s="10"/>
+      <c r="K149" s="10"/>
+      <c r="L149" s="11"/>
+    </row>
+    <row r="150" spans="2:16">
+      <c r="B150" s="9"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="10"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
+      <c r="G150" s="10"/>
+      <c r="H150" s="10"/>
+      <c r="I150" s="10"/>
+      <c r="J150" s="10"/>
+      <c r="K150" s="10"/>
+      <c r="L150" s="11"/>
+    </row>
+    <row r="151" spans="2:16">
+      <c r="B151" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11" t="s">
+      <c r="C151" s="10"/>
+      <c r="D151" s="10"/>
+      <c r="E151" s="10"/>
+      <c r="F151" s="10"/>
+      <c r="G151" s="10"/>
+      <c r="H151" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="J59" s="11"/>
-      <c r="K59" s="11"/>
-      <c r="L59" s="12"/>
-    </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B60" s="10" t="s">
+      <c r="J151" s="10"/>
+      <c r="K151" s="10"/>
+      <c r="L151" s="11"/>
+    </row>
+    <row r="152" spans="2:16">
+      <c r="B152" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="11"/>
-      <c r="L60" s="12"/>
-    </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B61" s="10" t="s">
+      <c r="C152" s="10"/>
+      <c r="D152" s="10"/>
+      <c r="E152" s="10"/>
+      <c r="F152" s="10"/>
+      <c r="G152" s="10"/>
+      <c r="H152" s="10"/>
+      <c r="I152" s="10"/>
+      <c r="J152" s="10"/>
+      <c r="K152" s="10"/>
+      <c r="L152" s="11"/>
+    </row>
+    <row r="153" spans="2:16">
+      <c r="B153" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="12"/>
-    </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B62" s="10" t="s">
+      <c r="C153" s="10"/>
+      <c r="D153" s="10"/>
+      <c r="E153" s="10"/>
+      <c r="F153" s="10"/>
+      <c r="G153" s="10"/>
+      <c r="H153" s="10"/>
+      <c r="I153" s="10"/>
+      <c r="J153" s="10"/>
+      <c r="K153" s="10"/>
+      <c r="L153" s="11"/>
+    </row>
+    <row r="154" spans="2:16">
+      <c r="B154" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="12"/>
-    </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B63" s="10"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="23" t="s">
+      <c r="C154" s="10"/>
+      <c r="D154" s="10"/>
+      <c r="E154" s="10"/>
+      <c r="F154" s="10"/>
+      <c r="G154" s="10"/>
+      <c r="I154" s="10"/>
+      <c r="J154" s="10"/>
+      <c r="K154" s="10"/>
+      <c r="L154" s="11"/>
+    </row>
+    <row r="155" spans="2:16">
+      <c r="B155" s="9"/>
+      <c r="C155" s="10"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="10"/>
+      <c r="H155" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="11"/>
-      <c r="L63" s="12"/>
-      <c r="M63" t="s">
+      <c r="I155" s="10"/>
+      <c r="J155" s="10"/>
+      <c r="K155" s="10"/>
+      <c r="L155" s="11"/>
+      <c r="M155" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B64" s="10" t="s">
+    <row r="156" spans="2:16">
+      <c r="B156" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
-      <c r="L64" s="12"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B65" s="10" t="s">
+      <c r="C156" s="10"/>
+      <c r="D156" s="10"/>
+      <c r="E156" s="10"/>
+      <c r="F156" s="10"/>
+      <c r="G156" s="10"/>
+      <c r="H156" s="10"/>
+      <c r="I156" s="10"/>
+      <c r="J156" s="10"/>
+      <c r="K156" s="10"/>
+      <c r="L156" s="11"/>
+    </row>
+    <row r="157" spans="2:16">
+      <c r="B157" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
-      <c r="L65" s="12"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B66" s="10"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="12"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B67" s="10" t="s">
+      <c r="C157" s="10"/>
+      <c r="D157" s="10"/>
+      <c r="E157" s="10"/>
+      <c r="F157" s="10"/>
+      <c r="G157" s="10"/>
+      <c r="H157" s="10"/>
+      <c r="I157" s="10"/>
+      <c r="J157" s="10"/>
+      <c r="K157" s="10"/>
+      <c r="L157" s="11"/>
+    </row>
+    <row r="158" spans="2:16">
+      <c r="B158" s="9"/>
+      <c r="C158" s="10"/>
+      <c r="D158" s="10"/>
+      <c r="E158" s="10"/>
+      <c r="F158" s="10"/>
+      <c r="G158" s="10"/>
+      <c r="H158" s="10"/>
+      <c r="I158" s="10"/>
+      <c r="J158" s="10"/>
+      <c r="K158" s="10"/>
+      <c r="L158" s="11"/>
+    </row>
+    <row r="159" spans="2:16">
+      <c r="B159" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11"/>
-      <c r="J67" s="11"/>
-      <c r="K67" s="11"/>
-      <c r="L67" s="12"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B68" s="10"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="11"/>
-      <c r="J68" s="11"/>
-      <c r="K68" s="11"/>
-      <c r="L68" s="12"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B69" s="16" t="s">
+      <c r="C159" s="10"/>
+      <c r="D159" s="10"/>
+      <c r="E159" s="10"/>
+      <c r="F159" s="10"/>
+      <c r="G159" s="10"/>
+      <c r="H159" s="10"/>
+      <c r="I159" s="10"/>
+      <c r="J159" s="10"/>
+      <c r="K159" s="10"/>
+      <c r="L159" s="11"/>
+    </row>
+    <row r="160" spans="2:16">
+      <c r="B160" s="9"/>
+      <c r="C160" s="10"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="10"/>
+      <c r="G160" s="10"/>
+      <c r="H160" s="10"/>
+      <c r="I160" s="10"/>
+      <c r="J160" s="10"/>
+      <c r="K160" s="10"/>
+      <c r="L160" s="11"/>
+    </row>
+    <row r="161" spans="2:12">
+      <c r="B161" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="11"/>
-      <c r="K69" s="11"/>
-      <c r="L69" s="12"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B70" s="16"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="12"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="10"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11" t="s">
+      <c r="C161" s="10"/>
+      <c r="D161" s="10"/>
+      <c r="E161" s="10"/>
+      <c r="F161" s="10"/>
+      <c r="G161" s="10"/>
+      <c r="H161" s="10"/>
+      <c r="I161" s="10"/>
+      <c r="J161" s="10"/>
+      <c r="K161" s="10"/>
+      <c r="L161" s="11"/>
+    </row>
+    <row r="162" spans="2:12">
+      <c r="B162" s="15"/>
+      <c r="C162" s="10"/>
+      <c r="D162" s="10"/>
+      <c r="E162" s="10"/>
+      <c r="F162" s="10"/>
+      <c r="G162" s="10"/>
+      <c r="H162" s="10"/>
+      <c r="I162" s="10"/>
+      <c r="J162" s="10"/>
+      <c r="K162" s="10"/>
+      <c r="L162" s="11"/>
+    </row>
+    <row r="163" spans="2:12">
+      <c r="B163" s="9"/>
+      <c r="C163" s="10"/>
+      <c r="D163" s="10"/>
+      <c r="E163" s="10"/>
+      <c r="F163" s="10"/>
+      <c r="G163" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="12"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B72" s="16" t="s">
+      <c r="H163" s="10"/>
+      <c r="I163" s="10"/>
+      <c r="J163" s="10"/>
+      <c r="K163" s="10"/>
+      <c r="L163" s="11"/>
+    </row>
+    <row r="164" spans="2:12">
+      <c r="B164" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="33" t="s">
+      <c r="C164" s="10"/>
+      <c r="D164" s="10"/>
+      <c r="E164" s="10"/>
+      <c r="F164" s="10"/>
+      <c r="G164" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="12"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B73" s="16"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="12"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B74" s="10" t="s">
+      <c r="H164" s="10"/>
+      <c r="I164" s="10"/>
+      <c r="J164" s="10"/>
+      <c r="K164" s="10"/>
+      <c r="L164" s="11"/>
+    </row>
+    <row r="165" spans="2:12">
+      <c r="B165" s="15"/>
+      <c r="C165" s="10"/>
+      <c r="D165" s="10"/>
+      <c r="E165" s="10"/>
+      <c r="F165" s="10"/>
+      <c r="G165" s="32"/>
+      <c r="H165" s="10"/>
+      <c r="I165" s="10"/>
+      <c r="J165" s="10"/>
+      <c r="K165" s="10"/>
+      <c r="L165" s="11"/>
+    </row>
+    <row r="166" spans="2:12">
+      <c r="B166" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" t="s">
+      <c r="C166" s="10"/>
+      <c r="D166" s="10"/>
+      <c r="E166" s="10"/>
+      <c r="F166" s="10"/>
+      <c r="G166" t="s">
         <v>221</v>
       </c>
-      <c r="H74" s="11"/>
-      <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11"/>
-      <c r="L74" s="12"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B75" s="10"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="34" t="s">
+      <c r="H166" s="10"/>
+      <c r="I166" s="10"/>
+      <c r="J166" s="10"/>
+      <c r="K166" s="10"/>
+      <c r="L166" s="11"/>
+    </row>
+    <row r="167" spans="2:12">
+      <c r="B167" s="9"/>
+      <c r="C167" s="10"/>
+      <c r="D167" s="10"/>
+      <c r="E167" s="10"/>
+      <c r="F167" s="10"/>
+      <c r="G167" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="H75" s="11"/>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11"/>
-      <c r="L75" s="12"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B76" s="10" t="s">
+      <c r="H167" s="10"/>
+      <c r="I167" s="10"/>
+      <c r="J167" s="10"/>
+      <c r="K167" s="10"/>
+      <c r="L167" s="11"/>
+    </row>
+    <row r="168" spans="2:12">
+      <c r="B168" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="H76" s="11"/>
-      <c r="I76" s="11"/>
-      <c r="J76" s="11"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="12"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B77" s="10" t="s">
+      <c r="C168" s="10"/>
+      <c r="D168" s="10"/>
+      <c r="E168" s="10"/>
+      <c r="F168" s="10"/>
+      <c r="H168" s="10"/>
+      <c r="I168" s="10"/>
+      <c r="J168" s="10"/>
+      <c r="K168" s="10"/>
+      <c r="L168" s="11"/>
+    </row>
+    <row r="169" spans="2:12">
+      <c r="B169" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="23" t="s">
+      <c r="C169" s="10"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="10"/>
+      <c r="F169" s="10"/>
+      <c r="G169" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="H77" s="11"/>
-      <c r="I77" s="11"/>
-      <c r="J77" s="11"/>
-      <c r="K77" s="11"/>
-      <c r="L77" s="12"/>
-    </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B78" s="10" t="s">
+      <c r="H169" s="10"/>
+      <c r="I169" s="10"/>
+      <c r="J169" s="10"/>
+      <c r="K169" s="10"/>
+      <c r="L169" s="11"/>
+    </row>
+    <row r="170" spans="2:12">
+      <c r="B170" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="12"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B79" s="10" t="s">
+      <c r="C170" s="10"/>
+      <c r="D170" s="10"/>
+      <c r="E170" s="10"/>
+      <c r="F170" s="10"/>
+      <c r="H170" s="10"/>
+      <c r="I170" s="10"/>
+      <c r="J170" s="10"/>
+      <c r="K170" s="10"/>
+      <c r="L170" s="11"/>
+    </row>
+    <row r="171" spans="2:12">
+      <c r="B171" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="11"/>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11"/>
-      <c r="L79" s="12"/>
-    </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B80" s="10" t="s">
+      <c r="C171" s="10"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="10"/>
+      <c r="F171" s="10"/>
+      <c r="G171" s="10"/>
+      <c r="H171" s="10"/>
+      <c r="I171" s="10"/>
+      <c r="J171" s="10"/>
+      <c r="K171" s="10"/>
+      <c r="L171" s="11"/>
+    </row>
+    <row r="172" spans="2:12">
+      <c r="B172" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
-      <c r="L80" s="12"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B81" s="10" t="s">
+      <c r="C172" s="10"/>
+      <c r="D172" s="10"/>
+      <c r="E172" s="10"/>
+      <c r="F172" s="10"/>
+      <c r="G172" s="10"/>
+      <c r="H172" s="10"/>
+      <c r="I172" s="10"/>
+      <c r="J172" s="10"/>
+      <c r="K172" s="10"/>
+      <c r="L172" s="11"/>
+    </row>
+    <row r="173" spans="2:12">
+      <c r="B173" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
-      <c r="L81" s="12"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B82" s="10" t="s">
+      <c r="C173" s="10"/>
+      <c r="D173" s="10"/>
+      <c r="E173" s="10"/>
+      <c r="F173" s="10"/>
+      <c r="G173" s="10"/>
+      <c r="H173" s="10"/>
+      <c r="I173" s="10"/>
+      <c r="J173" s="10"/>
+      <c r="K173" s="10"/>
+      <c r="L173" s="11"/>
+    </row>
+    <row r="174" spans="2:12">
+      <c r="B174" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
-      <c r="H82" s="11"/>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11"/>
-      <c r="K82" s="11"/>
-      <c r="L82" s="12"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B83" s="13" t="s">
+      <c r="C174" s="10"/>
+      <c r="D174" s="10"/>
+      <c r="E174" s="10"/>
+      <c r="F174" s="10"/>
+      <c r="G174" s="10"/>
+      <c r="H174" s="10"/>
+      <c r="I174" s="10"/>
+      <c r="J174" s="10"/>
+      <c r="K174" s="10"/>
+      <c r="L174" s="11"/>
+    </row>
+    <row r="175" spans="2:12">
+      <c r="B175" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14"/>
-      <c r="K83" s="14"/>
-      <c r="L83" s="15"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="D85" t="s">
+      <c r="C175" s="13"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="13"/>
+      <c r="F175" s="13"/>
+      <c r="G175" s="13"/>
+      <c r="H175" s="13"/>
+      <c r="I175" s="13"/>
+      <c r="J175" s="13"/>
+      <c r="K175" s="13"/>
+      <c r="L175" s="14"/>
+    </row>
+    <row r="177" spans="1:15">
+      <c r="D177" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="D86" t="s">
+    <row r="178" spans="1:15">
+      <c r="D178" t="s">
         <v>152</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F178" t="s">
         <v>153</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H178" t="s">
         <v>154</v>
       </c>
-      <c r="K86" t="s">
+      <c r="K178" t="s">
         <v>155</v>
       </c>
-      <c r="O86" t="s">
+      <c r="O178" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B87" s="25" t="s">
+    <row r="179" spans="1:15">
+      <c r="B179" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="C87" s="32" t="s">
+      <c r="C179" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="E87" s="5"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C88" s="6" t="s">
+      <c r="E179" s="4"/>
+    </row>
+    <row r="180" spans="1:15">
+      <c r="C180" s="5" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C89" t="s">
+    <row r="181" spans="1:15">
+      <c r="C181" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C90" s="6" t="s">
+    <row r="182" spans="1:15">
+      <c r="C182" s="5" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C91" s="6" t="s">
+    <row r="183" spans="1:15">
+      <c r="C183" s="5" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C92" s="32" t="s">
+    <row r="184" spans="1:15">
+      <c r="C184" s="31" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="D93" t="s">
+    <row r="185" spans="1:15">
+      <c r="D185" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+    <row r="188" spans="1:15">
+      <c r="A188" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B97" t="s">
+    <row r="189" spans="1:15">
+      <c r="B189" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B99" t="s">
+    <row r="191" spans="1:15">
+      <c r="B191" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B100" t="s">
+    <row r="192" spans="1:15">
+      <c r="B192" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B101" t="s">
+    <row r="193" spans="2:2">
+      <c r="B193" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B102" t="s">
+    <row r="194" spans="2:2">
+      <c r="B194" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B104" t="s">
+    <row r="196" spans="2:2">
+      <c r="B196" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B105" t="s">
+    <row r="197" spans="2:2">
+      <c r="B197" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B106" t="s">
+    <row r="198" spans="2:2">
+      <c r="B198" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B107" t="s">
+    <row r="199" spans="2:2">
+      <c r="B199" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B108" t="s">
+    <row r="200" spans="2:2">
+      <c r="B200" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B109" t="s">
+    <row r="201" spans="2:2">
+      <c r="B201" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B110" t="s">
+    <row r="202" spans="2:2">
+      <c r="B202" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B111" t="s">
+    <row r="203" spans="2:2">
+      <c r="B203" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B113" t="s">
+    <row r="205" spans="2:2">
+      <c r="B205" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B114" t="s">
+    <row r="206" spans="2:2">
+      <c r="B206" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B116" t="s">
+    <row r="208" spans="2:2">
+      <c r="B208" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B117" t="s">
+    <row r="209" spans="2:2">
+      <c r="B209" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B118" t="s">
+    <row r="210" spans="2:2">
+      <c r="B210" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B119" t="s">
+    <row r="211" spans="2:2">
+      <c r="B211" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B120" t="s">
+    <row r="212" spans="2:2">
+      <c r="B212" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B121" t="s">
+    <row r="213" spans="2:2">
+      <c r="B213" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B122" t="s">
+    <row r="214" spans="2:2">
+      <c r="B214" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B123" t="s">
+    <row r="215" spans="2:2">
+      <c r="B215" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B124" t="s">
+    <row r="216" spans="2:2">
+      <c r="B216" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B125" t="s">
+    <row r="217" spans="2:2">
+      <c r="B217" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B126" t="s">
+    <row r="218" spans="2:2">
+      <c r="B218" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B127" t="s">
+    <row r="219" spans="2:2">
+      <c r="B219" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B128" t="s">
+    <row r="220" spans="2:2">
+      <c r="B220" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B129" t="s">
+    <row r="221" spans="2:2">
+      <c r="B221" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B130" t="s">
+    <row r="222" spans="2:2">
+      <c r="B222" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B131" t="s">
+    <row r="223" spans="2:2">
+      <c r="B223" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B132" t="s">
+    <row r="224" spans="2:2">
+      <c r="B224" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B133" t="s">
+    <row r="225" spans="2:2">
+      <c r="B225" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B134" t="s">
+    <row r="226" spans="2:2">
+      <c r="B226" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B135" t="s">
+    <row r="227" spans="2:2">
+      <c r="B227" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B136" t="s">
+    <row r="228" spans="2:2">
+      <c r="B228" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B137" t="s">
+    <row r="229" spans="2:2">
+      <c r="B229" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B138" t="s">
+    <row r="230" spans="2:2">
+      <c r="B230" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B139" t="s">
+    <row r="231" spans="2:2">
+      <c r="B231" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B140" t="s">
+    <row r="232" spans="2:2">
+      <c r="B232" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B143" t="s">
+    <row r="235" spans="2:2">
+      <c r="B235" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B144" t="s">
+    <row r="236" spans="2:2">
+      <c r="B236" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B145" t="s">
+    <row r="237" spans="2:2">
+      <c r="B237" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B146" t="s">
+    <row r="238" spans="2:2">
+      <c r="B238" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B147" t="s">
+    <row r="239" spans="2:2">
+      <c r="B239" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B148" t="s">
+    <row r="240" spans="2:2">
+      <c r="B240" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B149" t="s">
+    <row r="241" spans="1:2">
+      <c r="B241" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B151" t="s">
+    <row r="243" spans="1:2">
+      <c r="B243" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B152" t="s">
+    <row r="244" spans="1:2">
+      <c r="B244" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B153" t="s">
+    <row r="245" spans="1:2">
+      <c r="B245" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B154" t="s">
+    <row r="246" spans="1:2">
+      <c r="B246" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B155" t="s">
+    <row r="247" spans="1:2">
+      <c r="B247" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B156" t="s">
+    <row r="248" spans="1:2">
+      <c r="B248" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B157" t="s">
+    <row r="249" spans="1:2">
+      <c r="B249" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B158" t="s">
+    <row r="250" spans="1:2">
+      <c r="B250" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B159" t="s">
+    <row r="251" spans="1:2">
+      <c r="B251" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B160" t="s">
+    <row r="252" spans="1:2">
+      <c r="B252" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
+    <row r="254" spans="1:2">
+      <c r="A254" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B163" t="s">
+    <row r="255" spans="1:2">
+      <c r="B255" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B165" t="s">
+    <row r="257" spans="2:2">
+      <c r="B257" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B166" t="s">
+    <row r="258" spans="2:2">
+      <c r="B258" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B167" t="s">
+    <row r="259" spans="2:2">
+      <c r="B259" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B168" t="s">
+    <row r="260" spans="2:2">
+      <c r="B260" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B170" t="s">
+    <row r="262" spans="2:2">
+      <c r="B262" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B171" t="s">
+    <row r="263" spans="2:2">
+      <c r="B263" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B172" t="s">
+    <row r="264" spans="2:2">
+      <c r="B264" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B173" t="s">
+    <row r="265" spans="2:2">
+      <c r="B265" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B174" t="s">
+    <row r="266" spans="2:2">
+      <c r="B266" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B175" t="s">
+    <row r="267" spans="2:2">
+      <c r="B267" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B176" t="s">
+    <row r="268" spans="2:2">
+      <c r="B268" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B178" t="s">
+    <row r="270" spans="2:2">
+      <c r="B270" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B179" t="s">
+    <row r="271" spans="2:2">
+      <c r="B271" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B181" t="s">
+    <row r="273" spans="2:2">
+      <c r="B273" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B182" t="s">
+    <row r="274" spans="2:2">
+      <c r="B274" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B183" t="s">
+    <row r="275" spans="2:2">
+      <c r="B275" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B184" t="s">
+    <row r="276" spans="2:2">
+      <c r="B276" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B185" t="s">
+    <row r="277" spans="2:2">
+      <c r="B277" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B186" t="s">
+    <row r="278" spans="2:2">
+      <c r="B278" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B187" t="s">
+    <row r="279" spans="2:2">
+      <c r="B279" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B188" t="s">
+    <row r="280" spans="2:2">
+      <c r="B280" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B189" t="s">
+    <row r="281" spans="2:2">
+      <c r="B281" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B190" t="s">
+    <row r="282" spans="2:2">
+      <c r="B282" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B191" t="s">
+    <row r="283" spans="2:2">
+      <c r="B283" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B192" t="s">
+    <row r="284" spans="2:2">
+      <c r="B284" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B193" t="s">
+    <row r="285" spans="2:2">
+      <c r="B285" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B194" t="s">
+    <row r="286" spans="2:2">
+      <c r="B286" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B195" t="s">
+    <row r="287" spans="2:2">
+      <c r="B287" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B196" t="s">
+    <row r="288" spans="2:2">
+      <c r="B288" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B197" t="s">
+    <row r="289" spans="2:2">
+      <c r="B289" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B198" t="s">
+    <row r="290" spans="2:2">
+      <c r="B290" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B199" t="s">
+    <row r="291" spans="2:2">
+      <c r="B291" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B200" t="s">
+    <row r="292" spans="2:2">
+      <c r="B292" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B201" t="s">
+    <row r="293" spans="2:2">
+      <c r="B293" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B202" t="s">
+    <row r="294" spans="2:2">
+      <c r="B294" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B203" t="s">
+    <row r="295" spans="2:2">
+      <c r="B295" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B204" t="s">
+    <row r="296" spans="2:2">
+      <c r="B296" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B205" t="s">
+    <row r="297" spans="2:2">
+      <c r="B297" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B207" t="s">
+    <row r="299" spans="2:2">
+      <c r="B299" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B208" t="s">
+    <row r="300" spans="2:2">
+      <c r="B300" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B209" t="s">
+    <row r="301" spans="2:2">
+      <c r="B301" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B210" t="s">
+    <row r="302" spans="2:2">
+      <c r="B302" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B211" t="s">
+    <row r="303" spans="2:2">
+      <c r="B303" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B212" t="s">
+    <row r="304" spans="2:2">
+      <c r="B304" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B213" t="s">
+    <row r="305" spans="1:2">
+      <c r="B305" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B215" t="s">
+    <row r="307" spans="1:2">
+      <c r="B307" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B216" t="s">
+    <row r="308" spans="1:2">
+      <c r="B308" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B217" t="s">
+    <row r="309" spans="1:2">
+      <c r="B309" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B218" t="s">
+    <row r="310" spans="1:2">
+      <c r="B310" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B219" t="s">
+    <row r="311" spans="1:2">
+      <c r="B311" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B220" t="s">
+    <row r="312" spans="1:2">
+      <c r="B312" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B221" t="s">
+    <row r="313" spans="1:2">
+      <c r="B313" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B222" t="s">
+    <row r="314" spans="1:2">
+      <c r="B314" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B223" t="s">
+    <row r="315" spans="1:2">
+      <c r="B315" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B224" t="s">
+    <row r="316" spans="1:2">
+      <c r="B316" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A226" s="3" t="s">
+    <row r="318" spans="1:2">
+      <c r="A318" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B227" t="s">
+    <row r="319" spans="1:2">
+      <c r="B319" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B228" t="s">
+    <row r="320" spans="1:2">
+      <c r="B320" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B229" t="s">
+    <row r="321" spans="2:7">
+      <c r="B321" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B231" s="38" t="s">
+    <row r="323" spans="2:7">
+      <c r="B323" s="37" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B233" s="38" t="s">
+    <row r="325" spans="2:7">
+      <c r="B325" s="37" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B235" t="s">
+    <row r="327" spans="2:7">
+      <c r="B327" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B237" t="s">
+    <row r="329" spans="2:7">
+      <c r="B329" t="s">
         <v>298</v>
       </c>
-      <c r="G237" t="s">
+      <c r="G329" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B238" t="s">
+    <row r="330" spans="2:7">
+      <c r="B330" t="s">
         <v>314</v>
       </c>
-      <c r="G238" t="s">
+      <c r="G330" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B240" s="38" t="s">
+    <row r="332" spans="2:7">
+      <c r="B332" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="G240" t="s">
+      <c r="G332" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="241" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B241" t="s">
+    <row r="333" spans="2:7">
+      <c r="B333" t="s">
         <v>292</v>
       </c>
-      <c r="G241" t="s">
+      <c r="G333" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="243" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B243" t="s">
+    <row r="335" spans="2:7">
+      <c r="B335" t="s">
         <v>300</v>
       </c>
-      <c r="G243" t="s">
+      <c r="G335" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="244" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B244" t="s">
+    <row r="336" spans="2:7">
+      <c r="B336" t="s">
         <v>293</v>
       </c>
-      <c r="G244" t="s">
+      <c r="G336" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="246" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B246" t="s">
+    <row r="338" spans="2:7">
+      <c r="B338" t="s">
         <v>301</v>
       </c>
-      <c r="G246" t="s">
+      <c r="G338" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="247" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B247" t="s">
+    <row r="339" spans="2:7">
+      <c r="B339" t="s">
         <v>302</v>
       </c>
-      <c r="G247" t="s">
+      <c r="G339" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="248" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B248" t="s">
+    <row r="340" spans="2:7">
+      <c r="B340" t="s">
         <v>303</v>
       </c>
-      <c r="G248" t="s">
+      <c r="G340" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="249" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B249" t="s">
+    <row r="341" spans="2:7">
+      <c r="B341" t="s">
         <v>305</v>
       </c>
-      <c r="G249" t="s">
+      <c r="G341" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="250" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B250" t="s">
+    <row r="342" spans="2:7">
+      <c r="B342" t="s">
         <v>307</v>
       </c>
-      <c r="G250" t="s">
+      <c r="G342" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="251" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B251" t="s">
+    <row r="343" spans="2:7">
+      <c r="B343" t="s">
         <v>309</v>
       </c>
-      <c r="G251" t="s">
+      <c r="G343" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="252" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B252" t="s">
+    <row r="344" spans="2:7">
+      <c r="B344" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="255" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B255" s="38" t="s">
+    <row r="347" spans="2:7">
+      <c r="B347" s="37" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="256" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B256" s="38" t="s">
+    <row r="348" spans="2:7">
+      <c r="B348" s="37" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B258" s="38" t="s">
+    <row r="350" spans="2:7">
+      <c r="B350" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="G258" s="39" t="s">
+      <c r="G350" s="38" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A261" s="3" t="s">
+    <row r="353" spans="1:12">
+      <c r="A353" s="3" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B263" t="s">
+    <row r="355" spans="1:12">
+      <c r="B355" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C264" s="25" t="s">
+    <row r="356" spans="1:12">
+      <c r="C356" s="24" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C265" t="s">
+    <row r="357" spans="1:12">
+      <c r="C357" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="I266" t="s">
+    <row r="358" spans="1:12">
+      <c r="I358" t="s">
         <v>272</v>
       </c>
-      <c r="L266" t="s">
+      <c r="L358" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C267" s="3" t="s">
+    <row r="359" spans="1:12">
+      <c r="C359" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I267" t="s">
+      <c r="I359" t="s">
         <v>273</v>
       </c>
-      <c r="L267" t="s">
+      <c r="L359" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D268" t="s">
+    <row r="360" spans="1:12">
+      <c r="D360" t="s">
         <v>259</v>
       </c>
-      <c r="I268" s="25" t="s">
+      <c r="I360" s="24" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D269" t="s">
+    <row r="361" spans="1:12">
+      <c r="D361" t="s">
         <v>261</v>
       </c>
-      <c r="I269" s="37" t="s">
+      <c r="I361" s="36" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D270" t="s">
+    <row r="362" spans="1:12">
+      <c r="D362" t="s">
         <v>258</v>
       </c>
-      <c r="I270" s="2">
+      <c r="I362" s="2">
         <v>764500</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B272" t="s">
+    <row r="364" spans="1:12">
+      <c r="B364" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="273" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C273" s="25" t="s">
+    <row r="365" spans="1:12">
+      <c r="C365" s="24" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="274" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C274" t="s">
+    <row r="366" spans="1:12">
+      <c r="C366" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="276" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C276" s="3" t="s">
+    <row r="368" spans="1:12">
+      <c r="C368" s="3" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="277" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D277" t="s">
+    <row r="369" spans="2:9">
+      <c r="D369" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="278" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D278" t="s">
+    <row r="370" spans="2:9">
+      <c r="D370" t="s">
         <v>266</v>
       </c>
-      <c r="I278" s="25" t="s">
+      <c r="I370" s="24" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="281" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B281" s="3" t="s">
+    <row r="373" spans="2:9">
+      <c r="B373" s="3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="282" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C282" s="25" t="s">
+    <row r="374" spans="2:9">
+      <c r="C374" s="24" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="283" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C283" t="s">
+    <row r="375" spans="2:9">
+      <c r="C375" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="284" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C284" t="s">
+    <row r="376" spans="2:9">
+      <c r="C376" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="285" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C285" t="s">
+    <row r="377" spans="2:9">
+      <c r="C377" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="286" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C286" t="s">
+    <row r="378" spans="2:9">
+      <c r="C378" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="288" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C288" s="3" t="s">
+    <row r="380" spans="2:9">
+      <c r="C380" s="3" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D289" t="s">
+    <row r="381" spans="2:9">
+      <c r="D381" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D291" t="s">
+    <row r="383" spans="2:9">
+      <c r="D383" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="E292" t="s">
+    <row r="384" spans="2:9">
+      <c r="E384" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="E293" t="s">
+    <row r="385" spans="3:7">
+      <c r="E385" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="E294" t="s">
+    <row r="386" spans="3:7">
+      <c r="E386" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="3" t="s">
+    <row r="388" spans="3:7">
+      <c r="C388" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D298" t="s">
+    <row r="390" spans="3:7">
+      <c r="D390" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="D299" t="s">
+    <row r="391" spans="3:7">
+      <c r="D391" t="s">
         <v>288</v>
       </c>
-      <c r="G299" t="s">
+      <c r="G391" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="G300" t="s">
+    <row r="392" spans="3:7">
+      <c r="G392" t="s">
         <v>290</v>
       </c>
     </row>
